--- a/templates/INFRA ADV CLA - template.xlsx
+++ b/templates/INFRA ADV CLA - template.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
@@ -1396,96 +1396,96 @@
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>111.34061899</v>
+        <v>111.946297</v>
       </c>
       <c r="D18" s="37" t="n">
-        <v>0.0005426570282978105</v>
+        <v>0.0005426525823497563</v>
       </c>
       <c r="E18" s="37" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F18" s="38" t="n">
-        <v>0.9999901751757684</v>
+        <v>0.9999819823317773</v>
       </c>
     </row>
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B19" s="39" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>111.28023199</v>
+        <v>111.885582</v>
       </c>
       <c r="D19" s="41" t="n">
-        <v>0.0005426637902632425</v>
+        <v>0.000542660897015379</v>
       </c>
       <c r="E19" s="41" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>1.000002635898922</v>
+        <v>0.9999973043187764</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B20" s="39" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>111.21987699</v>
+        <v>111.824899</v>
       </c>
       <c r="D20" s="41" t="n">
-        <v>0.0005426614023906762</v>
+        <v>0.0005426601130742448</v>
       </c>
       <c r="E20" s="41" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>0.9999982356074276</v>
+        <v>0.9999958596983416</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B21" s="39" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
-        <v>111.15955499</v>
+        <v>111.764249</v>
       </c>
       <c r="D21" s="41" t="n">
-        <v>0.0005426587606798261</v>
+        <v>0.0005426592575381584</v>
       </c>
       <c r="E21" s="41" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F21" s="42" t="n">
-        <v>0.9999933675512559</v>
+        <v>0.9999942831451297</v>
       </c>
     </row>
     <row r="22" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B22" s="39" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C22" s="40" t="n">
-        <v>111.099266</v>
+        <v>111.70363199</v>
       </c>
       <c r="D22" s="41" t="n">
-        <v>0.0005426561349926029</v>
+        <v>0.0005426670234593978</v>
       </c>
       <c r="E22" s="41" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F22" s="42" t="n">
-        <v>0.9999885290228865</v>
+        <v>1.00000859392438</v>
       </c>
     </row>
     <row r="23" ht="15.95" customHeight="1">
@@ -1525,18 +1525,18 @@
     <row r="25" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B25" s="43" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C25" s="43" t="inlineStr"/>
       <c r="D25" s="37" t="n">
-        <v>0.01048334796506567</v>
+        <v>0.003804801687054438</v>
       </c>
       <c r="E25" s="37" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F25" s="38" t="n">
-        <v>0.9999981398508258</v>
+        <v>0.9999935452152731</v>
       </c>
       <c r="G25" s="44" t="n"/>
     </row>
@@ -1549,13 +1549,13 @@
       </c>
       <c r="C26" s="54" t="inlineStr"/>
       <c r="D26" s="41" t="n">
-        <v>0.01159783106159362</v>
+        <v>0.01151037499818464</v>
       </c>
       <c r="E26" s="41" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F26" s="42" t="n">
-        <v>0.9999979305621864</v>
+        <v>0.9999960176392839</v>
       </c>
       <c r="G26" s="55" t="n"/>
     </row>
@@ -1568,13 +1568,13 @@
       </c>
       <c r="C27" s="54" t="inlineStr"/>
       <c r="D27" s="41" t="n">
-        <v>0.0352880920903258</v>
+        <v>0.03519858193310177</v>
       </c>
       <c r="E27" s="41" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F27" s="42" t="n">
-        <v>0.9999987056935978</v>
+        <v>0.9999978973272503</v>
       </c>
       <c r="G27" s="55" t="n"/>
     </row>
@@ -1587,13 +1587,13 @@
       </c>
       <c r="C28" s="54" t="inlineStr"/>
       <c r="D28" s="41" t="n">
-        <v>0.0718677557632259</v>
+        <v>0.07177508771469587</v>
       </c>
       <c r="E28" s="41" t="n">
-        <v>0.07186785093087189</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F28" s="42" t="n">
-        <v>0.9999986757966913</v>
+        <v>0.9999983316522235</v>
       </c>
       <c r="G28" s="55" t="n"/>
     </row>
@@ -1606,13 +1606,13 @@
       </c>
       <c r="C29" s="54" t="inlineStr"/>
       <c r="D29" s="41" t="n">
-        <v>0.0324389799871152</v>
+        <v>0.0380553093421836</v>
       </c>
       <c r="E29" s="41" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F29" s="42" t="n">
-        <v>0.9999986155560106</v>
+        <v>0.9999980309963429</v>
       </c>
       <c r="G29" s="55" t="n"/>
     </row>
@@ -1644,13 +1644,13 @@
       </c>
       <c r="C31" s="54" t="inlineStr"/>
       <c r="D31" s="41" t="n">
-        <v>0.1134061899000001</v>
+        <v>0.1194629700000001</v>
       </c>
       <c r="E31" s="41" t="n">
-        <v>0.1134063390652134</v>
+        <v>0.1194631520887273</v>
       </c>
       <c r="F31" s="42" t="n">
-        <v>0.9999986846836383</v>
+        <v>0.9999984757749647</v>
       </c>
       <c r="G31" s="55" t="n"/>
     </row>
@@ -1687,7 +1687,7 @@
       <c r="C35" s="14" t="n"/>
       <c r="D35" s="14" t="n"/>
       <c r="E35" s="48" t="n">
-        <v>254611458.32</v>
+        <v>252188582.68</v>
       </c>
       <c r="F35" s="29" t="n"/>
       <c r="G35" s="4" t="n"/>
@@ -1702,7 +1702,7 @@
       <c r="C36" s="14" t="n"/>
       <c r="D36" s="14" t="n"/>
       <c r="E36" s="48" t="n">
-        <v>235799315.0376531</v>
+        <v>236622827.143835</v>
       </c>
       <c r="F36" s="29" t="n"/>
       <c r="G36" s="4" t="n"/>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C38" s="19" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D38" s="20" t="n"/>
